--- a/Live Data From Sheet Via Apps Script.xlsx
+++ b/Live Data From Sheet Via Apps Script.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>QueryID</t>
   </si>
@@ -33,6 +33,9 @@
     <t>Likes</t>
   </si>
   <si>
+    <t>UserAvatar</t>
+  </si>
+  <si>
     <t>4/18/2026</t>
   </si>
   <si>
@@ -93,6 +96,24 @@
     <t>https://www.visionlearning.com/img/library/modules/mid109/Image/VLObject-2574-031204091253.gif</t>
   </si>
   <si>
+    <t>Hi</t>
+  </si>
+  <si>
+    <t>Gjv</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>https://graphaware.com/wp-content/uploads/2024/09/graph-analysis-1024x519.png.webp</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>https://biohub.org/wp-content/uploads/sites/32/2024/08/mark-zuckerberg@2x.png</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -114,7 +135,13 @@
     <t>Name</t>
   </si>
   <si>
+    <t>ProfilePicLink</t>
+  </si>
+  <si>
     <t>haldarsumit006@gmail.com</t>
+  </si>
+  <si>
+    <t>hello.sumithaldar@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -426,19 +453,22 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.713425E9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +479,10 @@
         <v>46129.955410243056</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -463,10 +493,10 @@
         <v>46129.95954603009</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -477,10 +507,10 @@
         <v>46129.97930041667</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3">
         <v>1.0</v>
@@ -494,10 +524,10 @@
         <v>46129.988101574076</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3">
         <v>3.0</v>
@@ -511,13 +541,13 @@
         <v>46129.99239921296</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3">
         <v>3.0</v>
@@ -531,13 +561,13 @@
         <v>46129.99897444445</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3">
         <v>0.0</v>
@@ -551,13 +581,13 @@
         <v>46130.00079907407</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3">
         <v>0.0</v>
@@ -571,20 +601,94 @@
         <v>46130.00303903935</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="4"/>
+      <c r="A11" s="3">
+        <v>1.776497123326E12</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46130.01763108796</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>1.776497140715E12</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46130.017832349535</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>1.776497336953E12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46130.020103622686</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>1.77649791021E12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46130.02673854167</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -592,8 +696,10 @@
     <hyperlink r:id="rId2" ref="E8"/>
     <hyperlink r:id="rId3" ref="E9"/>
     <hyperlink r:id="rId4" ref="E10"/>
+    <hyperlink r:id="rId5" ref="E13"/>
+    <hyperlink r:id="rId6" ref="G14"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -619,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -627,13 +733,13 @@
         <v>1.713425E9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -644,10 +750,10 @@
         <v>46129.95582096065</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -658,10 +764,10 @@
         <v>46129.95592094907</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -680,25 +786,47 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="30.5"/>
+    <col customWidth="1" min="3" max="3" width="25.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C2"/>
+    <hyperlink r:id="rId2" ref="C3"/>
+  </hyperlinks>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>